--- a/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_9_49.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_9_49.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4645890.57711045</v>
+        <v>4682200.354279868</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13275569.19337385</v>
+        <v>13279501.51514058</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13275569.19337385</v>
+        <v>13279501.51514058</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117101623</v>
+        <v>987.0883260128672</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117101623</v>
+        <v>987.0883260128672</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18806456.82317137</v>
+        <v>18805689.90910076</v>
       </c>
     </row>
   </sheetData>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>1.415908396047982</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>87.30283556964716</v>
+        <v>85.41253966162023</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -739,10 +739,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>374</v>
+        <v>268.7751300321497</v>
       </c>
       <c r="S3" t="n">
-        <v>374</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>158.1721839527246</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>87.30283556964716</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -979,19 +979,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>14.948158113322</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,19 +1015,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>133.6519859716245</v>
+        <v>255.7913883373922</v>
       </c>
       <c r="S6" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T6" t="n">
-        <v>4.473444462796863</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>4.363289606868648</v>
+        <v>6.316696067660079</v>
       </c>
       <c r="F8" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>87.30283556964716</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1252,22 +1252,22 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>133.6519859716245</v>
+        <v>374</v>
       </c>
       <c r="S9" t="n">
-        <v>364.8025280337897</v>
+        <v>374</v>
       </c>
       <c r="T9" t="n">
-        <v>4.473444462796863</v>
+        <v>143.5423005782355</v>
       </c>
       <c r="U9" t="n">
-        <v>374</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O10" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1380,13 +1380,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H11" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4605873653141466</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>158.5198244189524</v>
       </c>
       <c r="C12" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
         <v>26.93768689770263</v>
@@ -1459,10 +1459,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H12" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,31 +1489,31 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R12" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T12" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V12" t="n">
-        <v>267.1024830734933</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X12" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y12" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10.3217920922054</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M13" t="n">
         <v>102.3923982877958</v>
@@ -1565,16 +1565,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q13" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S13" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1681,19 +1681,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>237.1483725282995</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D15" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
         <v>3.99961134672543</v>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R15" t="n">
         <v>180.333570877285</v>
@@ -1741,16 +1741,16 @@
         <v>79.16168051490371</v>
       </c>
       <c r="V15" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>78.39139276613435</v>
+        <v>173.3546605387601</v>
       </c>
     </row>
     <row r="16">
@@ -1860,7 +1860,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S17" t="n">
         <v>142.3350019731772</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
         <v>40.09991244551929</v>
@@ -1927,7 +1927,7 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>21.67209722191262</v>
+        <v>116.6353649945385</v>
       </c>
       <c r="F18" t="n">
         <v>339.6362423378769</v>
@@ -1963,16 +1963,16 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R18" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S18" t="n">
-        <v>131.8202263797057</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T18" t="n">
-        <v>254.9671660051473</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U18" t="n">
         <v>79.16168051490371</v>
@@ -2158,7 +2158,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>40.09991244551929</v>
+        <v>135.063180218145</v>
       </c>
       <c r="D21" t="n">
         <v>347.9376868977026</v>
@@ -2173,7 +2173,7 @@
         <v>3.99961134672543</v>
       </c>
       <c r="H21" t="n">
-        <v>98.98524175149967</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2282,10 +2282,10 @@
         <v>352.895266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>376.871685410242</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S22" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>200.5295027796758</v>
+        <v>121.9009546703283</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F24" t="n">
         <v>18.63624233787687</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R24" t="n">
         <v>180.333570877285</v>
@@ -2452,16 +2452,16 @@
         <v>79.16168051490372</v>
       </c>
       <c r="V24" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W24" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2565,7 +2565,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H26" t="n">
         <v>72.84688483418068</v>
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>384.5565566463266</v>
+        <v>158.5198244189524</v>
       </c>
       <c r="C27" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
         <v>21.67209722191262</v>
@@ -2644,10 +2644,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H27" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2674,31 +2674,31 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R27" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S27" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T27" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V27" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W27" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>272.4545553273606</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M28" t="n">
         <v>102.3923982877958</v>
@@ -2750,13 +2750,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P28" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q28" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>376.8716854102422</v>
+        <v>376.871685410242</v>
       </c>
       <c r="S28" t="n">
         <v>30.56285675203577</v>
@@ -2835,10 +2835,10 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T29" t="n">
         <v>259.6218731858503</v>
@@ -2866,25 +2866,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F30" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H30" t="n">
-        <v>4.021973978873961</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2911,13 +2911,13 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R30" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>131.8202263797056</v>
+        <v>226.7834941523317</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
@@ -2935,7 +2935,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y30" t="n">
-        <v>251.9832086481073</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="31">
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M31" t="n">
         <v>102.3923982877958</v>
@@ -2990,7 +2990,7 @@
         <v>291.4220612627037</v>
       </c>
       <c r="Q31" t="n">
-        <v>352.895266425598</v>
+        <v>352.0570205760006</v>
       </c>
       <c r="R31" t="n">
         <v>377.7099312598396</v>
@@ -3039,7 +3039,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H32" t="n">
         <v>72.84688483418068</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>63.55655664632661</v>
+        <v>158.5198244189524</v>
       </c>
       <c r="C33" t="n">
         <v>40.09991244551929</v>
@@ -3118,10 +3118,10 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>177.5914272286987</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H33" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3148,31 +3148,31 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R33" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S33" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T33" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U33" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V33" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="34">
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M34" t="n">
         <v>102.3923982877958</v>
@@ -3224,16 +3224,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P34" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q34" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>376.8716854102422</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S34" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S35" t="n">
         <v>142.3350019731772</v>
@@ -3355,13 +3355,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H36" t="n">
-        <v>4.021973978873961</v>
+        <v>325.021973978874</v>
       </c>
       <c r="I36" t="n">
-        <v>173.5918158819732</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
         <v>180.333570877285</v>
@@ -3403,13 +3403,13 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>78.39139276613435</v>
+        <v>173.3546605387597</v>
       </c>
     </row>
     <row r="37">
@@ -3513,13 +3513,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H38" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T38" t="n">
         <v>259.6218731858503</v>
@@ -3577,28 +3577,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H39" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>94.96326777262568</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3622,31 +3622,31 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R39" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S39" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T39" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U39" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V39" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>284.9649587918018</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X39" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M40" t="n">
         <v>102.3923982877958</v>
@@ -3698,16 +3698,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P40" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q40" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S40" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3750,13 +3750,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H41" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3817,22 +3817,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H42" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3862,25 +3862,25 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
-        <v>275.2968386499106</v>
+        <v>275.2968386499108</v>
       </c>
       <c r="S42" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T42" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V42" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y42" t="n">
         <v>78.39139276613435</v>
@@ -3923,10 +3923,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M43" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N43" t="n">
         <v>155.2579933044718</v>
@@ -3935,16 +3935,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P43" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q43" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S43" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H44" t="n">
         <v>72.84688483418068</v>
@@ -4020,10 +4020,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T44" t="n">
         <v>259.6218731858503</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>237.1483725282995</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C45" t="n">
         <v>40.09991244551929</v>
@@ -4066,10 +4066,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>3.99961134672543</v>
+        <v>98.96287911935113</v>
       </c>
       <c r="H45" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4096,19 +4096,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T45" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M46" t="n">
         <v>102.3923982877958</v>
@@ -4172,16 +4172,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q46" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S46" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.914147375084</v>
+        <v>104.8416377852019</v>
       </c>
       <c r="C2" t="n">
-        <v>56.9398259175144</v>
+        <v>54.86731632763228</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426110047</v>
+        <v>44.42372467121835</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183921</v>
+        <v>40.01636143195709</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485754</v>
+        <v>35.07734253497542</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540306</v>
+        <v>33.64713203391685</v>
       </c>
       <c r="H2" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="I2" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>399.11</v>
       </c>
       <c r="K2" t="n">
-        <v>327.128108133742</v>
+        <v>451.2545884924623</v>
       </c>
       <c r="L2" t="n">
-        <v>697.388108133742</v>
+        <v>515.9445614572863</v>
       </c>
       <c r="M2" t="n">
-        <v>697.388108133742</v>
+        <v>694.7957936111288</v>
       </c>
       <c r="N2" t="n">
-        <v>697.388108133742</v>
+        <v>694.7957936111288</v>
       </c>
       <c r="O2" t="n">
-        <v>1067.648108133742</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="P2" t="n">
-        <v>1125.74</v>
+        <v>1122.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.815317606417</v>
+        <v>1405.724707412505</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.067250178448</v>
+        <v>1218.99441573196</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3617021698518</v>
+        <v>967.2891925799697</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1889504861913</v>
+        <v>735.1164408963092</v>
       </c>
       <c r="W2" t="n">
-        <v>496.4076616165473</v>
+        <v>494.3351520266652</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1835874138526</v>
+        <v>300.1110778239705</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.7417362190987</v>
+        <v>187.6692266292166</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>366.5169812739328</v>
+        <v>939.040343254833</v>
       </c>
       <c r="C3" t="n">
-        <v>366.5169812739328</v>
+        <v>939.040343254833</v>
       </c>
       <c r="D3" t="n">
-        <v>366.5169812739328</v>
+        <v>587.5881342672545</v>
       </c>
       <c r="E3" t="n">
-        <v>366.5169812739328</v>
+        <v>241.454702729969</v>
       </c>
       <c r="F3" t="n">
-        <v>366.5169812739328</v>
+        <v>241.454702729969</v>
       </c>
       <c r="G3" t="n">
-        <v>366.5169812739328</v>
+        <v>241.454702729969</v>
       </c>
       <c r="H3" t="n">
-        <v>33.13396963146437</v>
+        <v>241.454702729969</v>
       </c>
       <c r="I3" t="n">
-        <v>33.13396963146437</v>
+        <v>29.84</v>
       </c>
       <c r="J3" t="n">
-        <v>177.6113405614803</v>
+        <v>174.5185557413367</v>
       </c>
       <c r="K3" t="n">
-        <v>401.8775591086939</v>
+        <v>399.1286311753428</v>
       </c>
       <c r="L3" t="n">
-        <v>720.3885386284223</v>
+        <v>718.1019687139392</v>
       </c>
       <c r="M3" t="n">
-        <v>861.5031803712816</v>
+        <v>859.7561604567984</v>
       </c>
       <c r="N3" t="n">
-        <v>1051.274153846774</v>
+        <v>1046.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.994549492757</v>
+        <v>1337.587921002191</v>
       </c>
       <c r="P3" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.46108157432</v>
+        <v>1345.738421006376</v>
       </c>
       <c r="R3" t="n">
-        <v>971.6833037965423</v>
+        <v>1074.248390670872</v>
       </c>
       <c r="S3" t="n">
-        <v>593.9055260187645</v>
+        <v>1011.168735665642</v>
       </c>
       <c r="T3" t="n">
-        <v>434.1356432382346</v>
+        <v>1006.658862280313</v>
       </c>
       <c r="U3" t="n">
-        <v>433.9377383918481</v>
+        <v>1006.461100372748</v>
       </c>
       <c r="V3" t="n">
-        <v>419.2804988044541</v>
+        <v>991.8038607853543</v>
       </c>
       <c r="W3" t="n">
-        <v>386.5803544510919</v>
+        <v>959.1037164319922</v>
       </c>
       <c r="X3" t="n">
-        <v>366.5169812739328</v>
+        <v>939.040343254833</v>
       </c>
       <c r="Y3" t="n">
-        <v>366.5169812739328</v>
+        <v>939.040343254833</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>645.6418268795047</v>
+        <v>643.9580951932153</v>
       </c>
       <c r="C4" t="n">
-        <v>771.6438326979405</v>
+        <v>769.9601010116511</v>
       </c>
       <c r="D4" t="n">
-        <v>884.9629768229406</v>
+        <v>883.2792451366512</v>
       </c>
       <c r="E4" t="n">
-        <v>884.9629768229406</v>
+        <v>1001.108149348064</v>
       </c>
       <c r="F4" t="n">
-        <v>884.9629768229406</v>
+        <v>1001.108149348064</v>
       </c>
       <c r="G4" t="n">
-        <v>884.9629768229406</v>
+        <v>1154.698595562818</v>
       </c>
       <c r="H4" t="n">
-        <v>884.9629768229406</v>
+        <v>1154.698595562818</v>
       </c>
       <c r="I4" t="n">
-        <v>884.9629768229406</v>
+        <v>1381.361257449721</v>
       </c>
       <c r="J4" t="n">
-        <v>1255.222976822941</v>
+        <v>1381.361257449721</v>
       </c>
       <c r="K4" t="n">
-        <v>1386.743548464727</v>
+        <v>1381.361257449721</v>
       </c>
       <c r="L4" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1294.017231267251</v>
+        <v>1292.946305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.742122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>932.9209073660642</v>
+        <v>932.3861797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>665.0402361121327</v>
+        <v>664.7258098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3053387456568</v>
       </c>
       <c r="R4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="S4" t="n">
-        <v>70.34367574991084</v>
+        <v>70.29478771712391</v>
       </c>
       <c r="T4" t="n">
-        <v>70.34367574991084</v>
+        <v>70.29478771712391</v>
       </c>
       <c r="U4" t="n">
-        <v>184.0323053030732</v>
+        <v>122.2149930233984</v>
       </c>
       <c r="V4" t="n">
-        <v>382.8536981890192</v>
+        <v>321.0363859093444</v>
       </c>
       <c r="W4" t="n">
-        <v>382.8536981890192</v>
+        <v>492.9273041690218</v>
       </c>
       <c r="X4" t="n">
-        <v>533.8844892132126</v>
+        <v>643.9580951932153</v>
       </c>
       <c r="Y4" t="n">
-        <v>533.8844892132126</v>
+        <v>643.9580951932153</v>
       </c>
     </row>
     <row r="5">
@@ -4534,46 +4534,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106.914147375084</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C5" t="n">
-        <v>56.9398259175144</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D5" t="n">
-        <v>46.49623426110047</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E5" t="n">
-        <v>42.08887102183921</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F5" t="n">
-        <v>37.14985212485754</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G5" t="n">
-        <v>33.76871875540306</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>81.5583303517588</v>
+        <v>452.3245884924623</v>
       </c>
       <c r="L5" t="n">
-        <v>145.6202453266332</v>
+        <v>517.0145614572864</v>
       </c>
       <c r="M5" t="n">
-        <v>385.22</v>
+        <v>887.2745614572864</v>
       </c>
       <c r="N5" t="n">
-        <v>755.48</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O5" t="n">
-        <v>755.48</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P5" t="n">
         <v>1125.74</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T5" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U5" t="n">
-        <v>969.3617021698518</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V5" t="n">
-        <v>737.1889504861913</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W5" t="n">
-        <v>496.4076616165473</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X5" t="n">
-        <v>302.1835874138526</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y5" t="n">
-        <v>189.7417362190987</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1075.987801776748</v>
+        <v>724.4391204399794</v>
       </c>
       <c r="C6" t="n">
-        <v>1075.987801776748</v>
+        <v>724.4391204399794</v>
       </c>
       <c r="D6" t="n">
-        <v>724.5355927891701</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="E6" t="n">
-        <v>378.4021612518846</v>
+        <v>372.9869114524009</v>
       </c>
       <c r="F6" t="n">
-        <v>378.4021612518846</v>
+        <v>29.92</v>
       </c>
       <c r="G6" t="n">
-        <v>378.4021612518846</v>
+        <v>29.92</v>
       </c>
       <c r="H6" t="n">
-        <v>45.01914960941616</v>
+        <v>29.92</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K6" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N6" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1346.247111942856</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1211.245105910912</v>
+        <v>1237.424945633796</v>
       </c>
       <c r="S6" t="n">
-        <v>1148.125094511552</v>
+        <v>1174.345290628566</v>
       </c>
       <c r="T6" t="n">
-        <v>1143.60646374105</v>
+        <v>1169.835417243237</v>
       </c>
       <c r="U6" t="n">
-        <v>1143.408558894664</v>
+        <v>1169.637655335673</v>
       </c>
       <c r="V6" t="n">
-        <v>1128.75131930727</v>
+        <v>1154.980415748279</v>
       </c>
       <c r="W6" t="n">
-        <v>1096.051174953908</v>
+        <v>1122.280271394916</v>
       </c>
       <c r="X6" t="n">
-        <v>1075.987801776748</v>
+        <v>1102.216898217757</v>
       </c>
       <c r="Y6" t="n">
-        <v>1075.987801776748</v>
+        <v>1102.216898217757</v>
       </c>
     </row>
     <row r="7">
@@ -4692,52 +4692,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>909.9815649334121</v>
+        <v>253.0866383453244</v>
       </c>
       <c r="C7" t="n">
-        <v>1035.983570751848</v>
+        <v>379.0886441637601</v>
       </c>
       <c r="D7" t="n">
-        <v>1149.302714876848</v>
+        <v>492.4077882887602</v>
       </c>
       <c r="E7" t="n">
-        <v>1267.131619088261</v>
+        <v>610.2366925001733</v>
       </c>
       <c r="F7" t="n">
-        <v>1386.743548464727</v>
+        <v>734.5976650921087</v>
       </c>
       <c r="G7" t="n">
-        <v>1386.743548464727</v>
+        <v>888.1881113068629</v>
       </c>
       <c r="H7" t="n">
-        <v>1386.743548464727</v>
+        <v>1059.339559744949</v>
       </c>
       <c r="I7" t="n">
-        <v>1386.743548464727</v>
+        <v>1286.002221631852</v>
       </c>
       <c r="J7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P7" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
@@ -4749,19 +4749,19 @@
         <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>276.481125097303</v>
+        <v>29.92</v>
       </c>
       <c r="V7" t="n">
-        <v>475.302517983249</v>
+        <v>29.92</v>
       </c>
       <c r="W7" t="n">
-        <v>647.1934362429264</v>
+        <v>29.92</v>
       </c>
       <c r="X7" t="n">
-        <v>798.2242272671199</v>
+        <v>29.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>798.2242272671199</v>
+        <v>141.3293006790323</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106.914147375084</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C8" t="n">
-        <v>56.9398259175144</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D8" t="n">
-        <v>46.49623426110047</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E8" t="n">
-        <v>42.08887102183921</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F8" t="n">
-        <v>37.14985212485754</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G8" t="n">
-        <v>33.76871875540306</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4795,22 +4795,22 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>81.5583303517588</v>
+        <v>452.3245884924623</v>
       </c>
       <c r="L8" t="n">
-        <v>327.128108133742</v>
+        <v>822.5845884924622</v>
       </c>
       <c r="M8" t="n">
-        <v>697.388108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.648108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P8" t="n">
         <v>1125.74</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T8" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U8" t="n">
-        <v>969.3617021698518</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V8" t="n">
-        <v>737.1889504861913</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W8" t="n">
-        <v>496.4076616165473</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X8" t="n">
-        <v>302.1835874138526</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y8" t="n">
-        <v>189.7417362190987</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="9">
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.92</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="C9" t="n">
-        <v>29.92</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="D9" t="n">
         <v>29.92</v>
@@ -4874,52 +4874,52 @@
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K9" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L9" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M9" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N9" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P9" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1346.247111942856</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R9" t="n">
-        <v>1211.245105910912</v>
+        <v>971.7607285971344</v>
       </c>
       <c r="S9" t="n">
-        <v>842.7577038565788</v>
+        <v>593.9829508193566</v>
       </c>
       <c r="T9" t="n">
-        <v>838.2390730860769</v>
+        <v>448.9907280130581</v>
       </c>
       <c r="U9" t="n">
-        <v>460.4612953082991</v>
+        <v>448.7929661054938</v>
       </c>
       <c r="V9" t="n">
-        <v>82.68351753052127</v>
+        <v>434.1357265180997</v>
       </c>
       <c r="W9" t="n">
-        <v>49.98337317715914</v>
+        <v>401.4355821647376</v>
       </c>
       <c r="X9" t="n">
-        <v>29.92</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="Y9" t="n">
-        <v>29.92</v>
+        <v>381.3722089875785</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141.6773376662921</v>
+        <v>253.0866383453244</v>
       </c>
       <c r="C10" t="n">
-        <v>267.679343484728</v>
+        <v>379.0886441637601</v>
       </c>
       <c r="D10" t="n">
-        <v>380.998487609728</v>
+        <v>492.4077882887602</v>
       </c>
       <c r="E10" t="n">
-        <v>498.8273918211411</v>
+        <v>610.2366925001733</v>
       </c>
       <c r="F10" t="n">
-        <v>623.1883644130766</v>
+        <v>734.5976650921087</v>
       </c>
       <c r="G10" t="n">
-        <v>776.777025381929</v>
+        <v>888.1881113068629</v>
       </c>
       <c r="H10" t="n">
-        <v>947.9126013609987</v>
+        <v>1059.339559744949</v>
       </c>
       <c r="I10" t="n">
-        <v>1174.521576034786</v>
+        <v>1286.002221631852</v>
       </c>
       <c r="J10" t="n">
-        <v>1251.462556240126</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M10" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N10" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O10" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P10" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
@@ -4998,7 +4998,7 @@
         <v>29.92</v>
       </c>
       <c r="Y10" t="n">
-        <v>29.92</v>
+        <v>141.3293006790323</v>
       </c>
     </row>
     <row r="11">
@@ -5008,40 +5008,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C11" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D11" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E11" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F11" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G11" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H11" t="n">
-        <v>52.38523976294358</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I11" t="n">
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>310.7478922784252</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K11" t="n">
-        <v>953.2578922784252</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L11" t="n">
-        <v>1595.767892278425</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M11" t="n">
-        <v>2238.277892278425</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N11" t="n">
         <v>2238.277892278425</v>
@@ -5068,16 +5068,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W11" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X11" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="12">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>492.6952769985968</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C12" t="n">
         <v>127.9478906899915</v>
@@ -5099,10 +5099,10 @@
         <v>78.84709864997603</v>
       </c>
       <c r="F12" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G12" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5132,31 +5132,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q12" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R12" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S12" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T12" t="n">
-        <v>1846.683151095642</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U12" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V12" t="n">
-        <v>1496.92136969322</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W12" t="n">
-        <v>1384.423245541878</v>
+        <v>1156.103313999076</v>
       </c>
       <c r="X12" t="n">
-        <v>960.3194683243149</v>
+        <v>731.9995367815127</v>
       </c>
       <c r="Y12" t="n">
-        <v>881.1362433080176</v>
+        <v>328.5738875227911</v>
       </c>
     </row>
     <row r="13">
@@ -5196,25 +5196,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L13" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M13" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N13" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O13" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P13" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R13" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
@@ -5269,25 +5269,25 @@
         <v>51.92</v>
       </c>
       <c r="J14" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K14" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L14" t="n">
-        <v>991.9887866314309</v>
+        <v>1376.091327711023</v>
       </c>
       <c r="M14" t="n">
-        <v>1634.498786631431</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N14" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O14" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P14" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1141.180125483445</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C15" t="n">
-        <v>776.43273917484</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D15" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E15" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F15" t="n">
         <v>60.0226114399994</v>
@@ -5369,31 +5369,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q15" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R15" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S15" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T15" t="n">
-        <v>1846.683151095641</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U15" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V15" t="n">
-        <v>1672.26663826087</v>
+        <v>1268.601438150418</v>
       </c>
       <c r="W15" t="n">
-        <v>1559.768514109528</v>
+        <v>831.8608897566517</v>
       </c>
       <c r="X15" t="n">
-        <v>1459.907161134389</v>
+        <v>407.7571125390884</v>
       </c>
       <c r="Y15" t="n">
-        <v>1380.723936118091</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="16">
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C17" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D17" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E17" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F17" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G17" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H17" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
@@ -5509,16 +5509,16 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K17" t="n">
-        <v>1201.938527309012</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L17" t="n">
-        <v>1417.990475851726</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M17" t="n">
-        <v>1417.990475851726</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N17" t="n">
-        <v>1651.83297330616</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="O17" t="n">
         <v>1812.963074689115</v>
@@ -5530,28 +5530,28 @@
         <v>2596</v>
       </c>
       <c r="R17" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S17" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W17" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X17" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="18">
@@ -5561,13 +5561,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>816.9377012410209</v>
+        <v>912.8601939406431</v>
       </c>
       <c r="C18" t="n">
-        <v>776.4327391748399</v>
+        <v>872.355231874462</v>
       </c>
       <c r="D18" t="n">
-        <v>749.2229544296857</v>
+        <v>845.1454471293079</v>
       </c>
       <c r="E18" t="n">
         <v>727.3319471348245</v>
@@ -5606,31 +5606,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q18" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R18" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S18" t="n">
-        <v>1928.880474452383</v>
+        <v>1525.215274341931</v>
       </c>
       <c r="T18" t="n">
-        <v>1671.337882527992</v>
+        <v>1443.01795098519</v>
       </c>
       <c r="U18" t="n">
-        <v>1591.376589078594</v>
+        <v>1363.056657535792</v>
       </c>
       <c r="V18" t="n">
-        <v>1496.92136969322</v>
+        <v>1268.601438150418</v>
       </c>
       <c r="W18" t="n">
-        <v>1384.423245541878</v>
+        <v>1156.103313999076</v>
       </c>
       <c r="X18" t="n">
-        <v>1284.561892566739</v>
+        <v>1056.241961023937</v>
       </c>
       <c r="Y18" t="n">
-        <v>1205.378667550442</v>
+        <v>977.0587360076396</v>
       </c>
     </row>
     <row r="19">
@@ -5743,22 +5743,22 @@
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K20" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L20" t="n">
-        <v>523.631587033441</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M20" t="n">
-        <v>1166.141587033441</v>
+        <v>949.6332762537362</v>
       </c>
       <c r="N20" t="n">
-        <v>1170.453074689115</v>
+        <v>949.6332762537362</v>
       </c>
       <c r="O20" t="n">
-        <v>1812.963074689115</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="P20" t="n">
         <v>2009.555081027735</v>
@@ -5801,19 +5801,19 @@
         <v>1237.102618183067</v>
       </c>
       <c r="C21" t="n">
-        <v>1196.597656116886</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D21" t="n">
-        <v>845.1454471293077</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E21" t="n">
-        <v>499.0120155920222</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F21" t="n">
-        <v>155.9451041396213</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G21" t="n">
-        <v>151.9050926782825</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5925,7 +5925,7 @@
         <v>463.4700425881595</v>
       </c>
       <c r="R22" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5980,25 +5980,25 @@
         <v>51.92</v>
       </c>
       <c r="J23" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K23" t="n">
-        <v>775.9368380887173</v>
+        <v>989.863031102066</v>
       </c>
       <c r="L23" t="n">
-        <v>1418.446838088717</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="M23" t="n">
-        <v>1595.767892278425</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="N23" t="n">
-        <v>2238.277892278425</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O23" t="n">
-        <v>2399.40799366138</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P23" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q23" t="n">
         <v>2596</v>
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>668.0405455662465</v>
+        <v>264.3753454557945</v>
       </c>
       <c r="C24" t="n">
-        <v>627.5355835000654</v>
+        <v>223.8703833896134</v>
       </c>
       <c r="D24" t="n">
-        <v>424.9805301872615</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E24" t="n">
         <v>78.84709864997603</v>
@@ -6080,31 +6080,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q24" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R24" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S24" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T24" t="n">
-        <v>1846.683151095642</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U24" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V24" t="n">
-        <v>1672.26663826087</v>
+        <v>1268.601438150418</v>
       </c>
       <c r="W24" t="n">
-        <v>1559.768514109528</v>
+        <v>831.8608897566517</v>
       </c>
       <c r="X24" t="n">
-        <v>1135.664736891965</v>
+        <v>731.9995367815127</v>
       </c>
       <c r="Y24" t="n">
-        <v>732.239087633243</v>
+        <v>652.8163117652153</v>
       </c>
     </row>
     <row r="25">
@@ -6205,7 +6205,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F26" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G26" t="n">
         <v>125.5027119537179</v>
@@ -6220,13 +6220,13 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K26" t="n">
-        <v>1201.938527309012</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L26" t="n">
-        <v>1417.990475851726</v>
+        <v>1376.091327711023</v>
       </c>
       <c r="M26" t="n">
-        <v>1595.767892278425</v>
+        <v>2018.601327711023</v>
       </c>
       <c r="N26" t="n">
         <v>2238.277892278425</v>
@@ -6272,10 +6272,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>816.9377012410212</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C27" t="n">
-        <v>452.1903149324157</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D27" t="n">
         <v>100.7381059448373</v>
@@ -6284,10 +6284,10 @@
         <v>78.84709864997603</v>
       </c>
       <c r="F27" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G27" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H27" t="n">
         <v>51.92</v>
@@ -6317,31 +6317,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q27" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R27" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S27" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T27" t="n">
-        <v>1846.683151095642</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U27" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V27" t="n">
-        <v>1672.26663826087</v>
+        <v>1268.601438150418</v>
       </c>
       <c r="W27" t="n">
-        <v>1559.768514109528</v>
+        <v>1156.103313999076</v>
       </c>
       <c r="X27" t="n">
-        <v>1284.561892566739</v>
+        <v>731.9995367815127</v>
       </c>
       <c r="Y27" t="n">
-        <v>1205.378667550442</v>
+        <v>328.5738875227911</v>
       </c>
     </row>
     <row r="28">
@@ -6393,10 +6393,10 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P28" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R28" t="n">
         <v>82.79157247680381</v>
@@ -6457,28 +6457,28 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K29" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L29" t="n">
-        <v>950.0896384907273</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M29" t="n">
-        <v>1592.599638490728</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N29" t="n">
-        <v>2235.109638490728</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O29" t="n">
-        <v>2396.239739873683</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P29" t="n">
-        <v>2592.831746212303</v>
+        <v>2596</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S29" t="n">
         <v>2451.762030971221</v>
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>816.9377012410212</v>
+        <v>816.937701241021</v>
       </c>
       <c r="C30" t="n">
-        <v>452.1903149324157</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D30" t="n">
-        <v>424.9805301872615</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E30" t="n">
-        <v>78.84709864997603</v>
+        <v>727.3319471348246</v>
       </c>
       <c r="F30" t="n">
-        <v>60.02261143999941</v>
+        <v>708.507459924848</v>
       </c>
       <c r="G30" t="n">
-        <v>55.98259997866057</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6554,31 +6554,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q30" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R30" t="n">
-        <v>2062.032218270268</v>
+        <v>1658.367018159816</v>
       </c>
       <c r="S30" t="n">
-        <v>1928.880474452383</v>
+        <v>1429.292781642309</v>
       </c>
       <c r="T30" t="n">
-        <v>1846.683151095642</v>
+        <v>1347.095458285567</v>
       </c>
       <c r="U30" t="n">
-        <v>1766.721857646244</v>
+        <v>1267.13416483617</v>
       </c>
       <c r="V30" t="n">
-        <v>1672.26663826087</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W30" t="n">
-        <v>1559.768514109528</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X30" t="n">
-        <v>1459.907161134389</v>
+        <v>960.3194683243149</v>
       </c>
       <c r="Y30" t="n">
-        <v>1205.378667550442</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="31">
@@ -6618,19 +6618,19 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L31" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M31" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N31" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O31" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P31" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q31" t="n">
         <v>464.3167555675509</v>
@@ -6679,7 +6679,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F32" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G32" t="n">
         <v>125.5027119537179</v>
@@ -6691,25 +6691,25 @@
         <v>51.92</v>
       </c>
       <c r="J32" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K32" t="n">
-        <v>737.2059437357115</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L32" t="n">
-        <v>953.2578922784251</v>
+        <v>1170.453074689115</v>
       </c>
       <c r="M32" t="n">
-        <v>1595.767892278425</v>
+        <v>1170.453074689115</v>
       </c>
       <c r="N32" t="n">
-        <v>2238.277892278425</v>
+        <v>1170.453074689115</v>
       </c>
       <c r="O32" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P32" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>343.7981213238224</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C33" t="n">
-        <v>303.2931592576413</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D33" t="n">
-        <v>276.0833745124871</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E33" t="n">
-        <v>254.1923672176258</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F33" t="n">
-        <v>235.3678800076492</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G33" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H33" t="n">
         <v>51.92</v>
@@ -6791,31 +6791,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q33" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R33" t="n">
-        <v>1737.789794027844</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S33" t="n">
-        <v>1280.395625967535</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T33" t="n">
-        <v>873.9558783683688</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U33" t="n">
-        <v>793.9945849189711</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V33" t="n">
-        <v>699.5393655335972</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W33" t="n">
-        <v>587.0412413822553</v>
+        <v>1156.103313999076</v>
       </c>
       <c r="X33" t="n">
-        <v>487.1798884071163</v>
+        <v>731.9995367815127</v>
       </c>
       <c r="Y33" t="n">
-        <v>407.996663390819</v>
+        <v>328.5738875227911</v>
       </c>
     </row>
     <row r="34">
@@ -6867,13 +6867,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P34" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q34" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R34" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S34" t="n">
         <v>51.92</v>
@@ -6904,40 +6904,40 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C35" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D35" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E35" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F35" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G35" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H35" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I35" t="n">
         <v>51.92</v>
       </c>
       <c r="J35" t="n">
-        <v>559.4285273090126</v>
+        <v>150.7610247634461</v>
       </c>
       <c r="K35" t="n">
-        <v>733.5813277110226</v>
+        <v>793.271024763446</v>
       </c>
       <c r="L35" t="n">
-        <v>949.6332762537361</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="M35" t="n">
-        <v>1592.143276253736</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N35" t="n">
         <v>1651.83297330616</v>
@@ -6952,28 +6952,28 @@
         <v>2596</v>
       </c>
       <c r="R35" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S35" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T35" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U35" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V35" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W35" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X35" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y35" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="36">
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>668.0405455662465</v>
+        <v>1141.180125483446</v>
       </c>
       <c r="C36" t="n">
-        <v>627.5355835000654</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D36" t="n">
-        <v>600.3257987549113</v>
+        <v>1073.46537867211</v>
       </c>
       <c r="E36" t="n">
-        <v>578.4347914600501</v>
+        <v>1051.574371377249</v>
       </c>
       <c r="F36" t="n">
-        <v>235.3678800076491</v>
+        <v>708.507459924848</v>
       </c>
       <c r="G36" t="n">
-        <v>231.3278685463103</v>
+        <v>380.2250242210849</v>
       </c>
       <c r="H36" t="n">
-        <v>227.2652685676497</v>
+        <v>51.92</v>
       </c>
       <c r="I36" t="n">
         <v>51.92</v>
@@ -7028,31 +7028,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q36" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R36" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S36" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T36" t="n">
-        <v>1846.683151095642</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U36" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V36" t="n">
-        <v>1672.26663826087</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W36" t="n">
-        <v>1235.526089867104</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X36" t="n">
-        <v>811.4223126495403</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y36" t="n">
-        <v>732.239087633243</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="37">
@@ -7141,25 +7141,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C38" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D38" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E38" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F38" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G38" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H38" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I38" t="n">
         <v>51.92</v>
@@ -7171,19 +7171,19 @@
         <v>307.5796384907274</v>
       </c>
       <c r="L38" t="n">
-        <v>523.631587033441</v>
+        <v>950.0896384907273</v>
       </c>
       <c r="M38" t="n">
-        <v>668.47</v>
+        <v>1592.599638490728</v>
       </c>
       <c r="N38" t="n">
-        <v>1310.98</v>
+        <v>2235.109638490728</v>
       </c>
       <c r="O38" t="n">
-        <v>1953.49</v>
+        <v>2396.239739873683</v>
       </c>
       <c r="P38" t="n">
-        <v>2596</v>
+        <v>2592.831746212303</v>
       </c>
       <c r="Q38" t="n">
         <v>2596</v>
@@ -7192,25 +7192,25 @@
         <v>2596</v>
       </c>
       <c r="S38" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T38" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U38" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V38" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W38" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X38" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y38" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="39">
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>816.937701241021</v>
+        <v>912.8601939406431</v>
       </c>
       <c r="C39" t="n">
-        <v>776.43273917484</v>
+        <v>548.1128076320376</v>
       </c>
       <c r="D39" t="n">
-        <v>749.2229544296858</v>
+        <v>520.9030228868835</v>
       </c>
       <c r="E39" t="n">
-        <v>403.0895228924003</v>
+        <v>499.0120155920222</v>
       </c>
       <c r="F39" t="n">
-        <v>60.02261143999941</v>
+        <v>155.9451041396213</v>
       </c>
       <c r="G39" t="n">
-        <v>55.98259997866057</v>
+        <v>151.9050926782825</v>
       </c>
       <c r="H39" t="n">
-        <v>51.92</v>
+        <v>147.8424926996219</v>
       </c>
       <c r="I39" t="n">
         <v>51.92</v>
@@ -7265,31 +7265,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q39" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R39" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S39" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T39" t="n">
-        <v>1846.683151095642</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U39" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V39" t="n">
-        <v>1672.26663826087</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W39" t="n">
-        <v>1384.423245541878</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X39" t="n">
-        <v>1284.561892566739</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y39" t="n">
-        <v>881.1362433080176</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="40">
@@ -7341,13 +7341,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P40" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q40" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R40" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S40" t="n">
         <v>51.92</v>
@@ -7378,25 +7378,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C41" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D41" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E41" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F41" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H41" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I41" t="n">
         <v>51.92</v>
@@ -7411,13 +7411,13 @@
         <v>949.6332762537361</v>
       </c>
       <c r="M41" t="n">
-        <v>1592.143276253736</v>
+        <v>949.6332762537362</v>
       </c>
       <c r="N41" t="n">
-        <v>1651.83297330616</v>
+        <v>949.6332762537362</v>
       </c>
       <c r="O41" t="n">
-        <v>1812.963074689115</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P41" t="n">
         <v>2009.555081027735</v>
@@ -7438,16 +7438,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W41" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X41" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1141.180125483445</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C42" t="n">
-        <v>1100.675163417264</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D42" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E42" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F42" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G42" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H42" t="n">
         <v>51.92</v>
@@ -7508,7 +7508,7 @@
         <v>1886.686949702618</v>
       </c>
       <c r="S42" t="n">
-        <v>1753.535205884734</v>
+        <v>1753.535205884733</v>
       </c>
       <c r="T42" t="n">
         <v>1671.337882527992</v>
@@ -7517,16 +7517,16 @@
         <v>1591.376589078594</v>
       </c>
       <c r="V42" t="n">
-        <v>1496.92136969322</v>
+        <v>1172.678945450796</v>
       </c>
       <c r="W42" t="n">
-        <v>1384.423245541878</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X42" t="n">
-        <v>1284.561892566739</v>
+        <v>636.0770440818907</v>
       </c>
       <c r="Y42" t="n">
-        <v>1205.378667550442</v>
+        <v>556.8938190655933</v>
       </c>
     </row>
     <row r="43">
@@ -7569,22 +7569,22 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M43" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N43" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O43" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P43" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7627,7 +7627,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F44" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G44" t="n">
         <v>125.5027119537179</v>
@@ -7645,7 +7645,7 @@
         <v>307.5796384907274</v>
       </c>
       <c r="L44" t="n">
-        <v>950.0896384907273</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M44" t="n">
         <v>1009.32297330616</v>
@@ -7663,7 +7663,7 @@
         <v>2596</v>
       </c>
       <c r="R44" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S44" t="n">
         <v>2451.762030971221</v>
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1141.180125483445</v>
+        <v>1237.102618183067</v>
       </c>
       <c r="C45" t="n">
-        <v>1100.675163417264</v>
+        <v>1196.597656116886</v>
       </c>
       <c r="D45" t="n">
-        <v>749.2229544296858</v>
+        <v>845.1454471293077</v>
       </c>
       <c r="E45" t="n">
-        <v>403.0895228924003</v>
+        <v>499.0120155920222</v>
       </c>
       <c r="F45" t="n">
-        <v>60.0226114399994</v>
+        <v>155.9451041396213</v>
       </c>
       <c r="G45" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H45" t="n">
         <v>51.92</v>
@@ -7739,31 +7739,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q45" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R45" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S45" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T45" t="n">
-        <v>1846.683151095641</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U45" t="n">
-        <v>1766.721857646244</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V45" t="n">
-        <v>1672.26663826087</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W45" t="n">
-        <v>1559.768514109528</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X45" t="n">
-        <v>1459.907161134389</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y45" t="n">
-        <v>1380.723936118091</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="46">
@@ -7803,25 +7803,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L46" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M46" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N46" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O46" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P46" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q46" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R46" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S46" t="n">
         <v>51.92</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>372.8993027275024</v>
       </c>
       <c r="K2" t="n">
-        <v>248.0502805878618</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>309.2909949748744</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>472.2608914614128</v>
+        <v>652.2128072454574</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>375.1590153027356</v>
+        <v>373.4816735941929</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>502.5418702571336</v>
+        <v>501.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8055,7 +8055,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N3" t="n">
-        <v>485.4085271713503</v>
+        <v>481.6508651829305</v>
       </c>
       <c r="O3" t="n">
         <v>382.6817988009037</v>
@@ -8201,7 +8201,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -8210,19 +8210,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>714.2808456769349</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N5" t="n">
-        <v>778.0826666125488</v>
+        <v>584.9827562456367</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
-        <v>315.3213213472141</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2405037325275146</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>183.3412755627362</v>
+        <v>308.6565929648241</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>718.5158102402294</v>
       </c>
       <c r="N8" t="n">
-        <v>778.0826666125488</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,7 +8675,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>179.1121759491998</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>473.0880804020101</v>
@@ -8687,7 +8687,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N11" t="n">
-        <v>230.4920535472222</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>430.7657085427137</v>
       </c>
       <c r="M14" t="n">
-        <v>950.4344291498551</v>
+        <v>579.9613438924174</v>
       </c>
       <c r="N14" t="n">
-        <v>840.3699380391354</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9152,19 +9152,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>473.08808040201</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N17" t="n">
-        <v>466.6965964304885</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>60.29262328527628</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -9386,7 +9386,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -9395,16 +9395,16 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N20" t="n">
-        <v>234.8470915832563</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O20" t="n">
         <v>486.2423218353989</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>223.0503014498774</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9623,28 +9623,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>473.0880804020101</v>
+        <v>258.8704074657004</v>
       </c>
       <c r="L23" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>480.5466050990546</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N23" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,16 +9863,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>473.08808040201</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>430.7657085427137</v>
       </c>
       <c r="M26" t="n">
-        <v>481.0075770556116</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N26" t="n">
-        <v>879.4920535472222</v>
+        <v>452.3875733122749</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -10100,7 +10100,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L29" t="n">
         <v>430.7657085427136</v>
@@ -10109,7 +10109,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>879.4920535472222</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>26.68372459829277</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,28 +10334,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>433.9659648939233</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>223.0503014498773</v>
       </c>
       <c r="M32" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N32" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,10 +10571,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>17.50927946942296</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -10583,7 +10583,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N35" t="n">
-        <v>290.7846768324985</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10814,22 +10814,22 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M38" t="n">
-        <v>447.7358563888035</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N38" t="n">
         <v>879.4920535472222</v>
       </c>
       <c r="O38" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>23.48346824708341</v>
+        <v>26.68372459829277</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11054,16 +11054,16 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N41" t="n">
-        <v>290.7846768324985</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>258.8704074657004</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11288,10 +11288,10 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>361.2660804785743</v>
+        <v>792.031789021288</v>
       </c>
       <c r="N44" t="n">
         <v>879.4920535472222</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.927393539209461</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -24140,10 +24140,10 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24614,7 +24614,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24848,7 +24848,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -25088,10 +25088,10 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25784,7 +25784,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26018,7 +26018,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -26039,7 +26039,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>734756.8010130918</v>
+        <v>734487.1092780825</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1395929.747187704</v>
+        <v>1395766.8199117</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2057102.693362317</v>
+        <v>2056939.766086313</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2717830.754639224</v>
+        <v>2717750.208863221</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3378993.138916132</v>
+        <v>3378912.593140129</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4040155.523193039</v>
+        <v>4040074.977417035</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4701317.907469943</v>
+        <v>4701237.36169394</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5362480.291746847</v>
+        <v>5362399.745970844</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6023642.676023752</v>
+        <v>6023562.130247748</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6684805.060300657</v>
+        <v>6684724.514524654</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7345967.444577566</v>
+        <v>7345886.898801563</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8007129.828854479</v>
+        <v>8007049.283078476</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8668292.213131392</v>
+        <v>8668211.667355388</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9329454.597408304</v>
+        <v>9329374.0516323</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9990616.981685216</v>
+        <v>9990536.435909213</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1542736.874407429</v>
+        <v>1542548.93426342</v>
       </c>
       <c r="C2" t="n">
         <v>1542736.874407429</v>
@@ -26278,16 +26278,16 @@
         <v>1542736.874407429</v>
       </c>
       <c r="E2" t="n">
-        <v>1542712.229979452</v>
+        <v>1542712.229979451</v>
       </c>
       <c r="F2" t="n">
-        <v>1542712.22997945</v>
+        <v>1542712.229979451</v>
       </c>
       <c r="G2" t="n">
         <v>1542712.22997945</v>
       </c>
       <c r="H2" t="n">
-        <v>1542712.22997945</v>
+        <v>1542712.229979451</v>
       </c>
       <c r="I2" t="n">
         <v>1542712.229979452</v>
@@ -26299,16 +26299,16 @@
         <v>1542712.229979451</v>
       </c>
       <c r="L2" t="n">
-        <v>1542712.229979452</v>
+        <v>1542712.229979451</v>
       </c>
       <c r="M2" t="n">
         <v>1542712.229979452</v>
       </c>
       <c r="N2" t="n">
-        <v>1542712.229979452</v>
+        <v>1542712.22997945</v>
       </c>
       <c r="O2" t="n">
-        <v>1542712.229979452</v>
+        <v>1542712.229979451</v>
       </c>
       <c r="P2" t="n">
         <v>1542712.229979451</v>
@@ -26321,16 +26321,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231098</v>
+        <v>231721</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>589550</v>
+        <v>588575</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,10 +26345,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448</v>
+        <v>388096</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570823.1065049333</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568738.1032495913</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634525</v>
+        <v>566727.0147207878</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.979796175</v>
+        <v>483475.9886658208</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779522</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457892</v>
+        <v>476717.710215435</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286013</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.6099301391</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26425,13 +26425,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58590.39999999999</v>
+        <v>58551.39999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="D5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="E5" t="n">
         <v>73944.549</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>675583.5397406638</v>
+        <v>681453.4277584869</v>
       </c>
       <c r="C6" t="n">
-        <v>908690.4619281526</v>
+        <v>915034.5711578373</v>
       </c>
       <c r="D6" t="n">
-        <v>910702.1093439765</v>
+        <v>917397.6596866413</v>
       </c>
       <c r="E6" t="n">
-        <v>389278.7011832765</v>
+        <v>396716.6923136298</v>
       </c>
       <c r="F6" t="n">
-        <v>980514.7640014981</v>
+        <v>986977.7551318532</v>
       </c>
       <c r="G6" t="n">
-        <v>982203.1535231514</v>
+        <v>988666.1446535055</v>
       </c>
       <c r="H6" t="n">
-        <v>983893.8864331137</v>
+        <v>990356.8775634683</v>
       </c>
       <c r="I6" t="n">
-        <v>985586.9796336625</v>
+        <v>992049.9707640168</v>
       </c>
       <c r="J6" t="n">
-        <v>598834.4502485868</v>
+        <v>605649.4413789406</v>
       </c>
       <c r="K6" t="n">
-        <v>988980.3156274197</v>
+        <v>995091.3067577741</v>
       </c>
       <c r="L6" t="n">
-        <v>990680.5933497645</v>
+        <v>997143.5844801177</v>
       </c>
       <c r="M6" t="n">
-        <v>895583.3012297322</v>
+        <v>902046.2923600866</v>
       </c>
       <c r="N6" t="n">
-        <v>994088.4573204961</v>
+        <v>1000551.448450849</v>
       </c>
       <c r="O6" t="n">
-        <v>738996.0799189582</v>
+        <v>745459.0710493118</v>
       </c>
       <c r="P6" t="n">
-        <v>997506.1875705408</v>
+        <v>1003969.178700896</v>
       </c>
     </row>
   </sheetData>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
         <v>344</v>
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
         <v>374</v>
@@ -26990,7 +26990,7 @@
         <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -26999,16 +26999,16 @@
         <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27076,10 +27076,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27100,10 +27100,10 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -27317,10 +27317,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
-        <v>398.2013121321733</v>
+        <v>399.9999999999992</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27518,22 +27518,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27560,13 +27560,13 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>159.6519859716246</v>
+        <v>264.7433087696634</v>
       </c>
       <c r="S3" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>246.3012605100723</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27591,7 +27591,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
         <v>400</v>
@@ -27600,28 +27600,28 @@
         <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1357818393235</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I4" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>396.2647849014816</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K4" t="n">
+        <v>266.941429538848</v>
+      </c>
+      <c r="L4" t="n">
         <v>400</v>
-      </c>
-      <c r="L4" t="n">
-        <v>396.2015953708939</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27645,16 +27645,16 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2386648669134</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U4" t="n">
-        <v>265.7853580362216</v>
+        <v>203.3929119514367</v>
       </c>
       <c r="V4" t="n">
         <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
         <v>400</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,10 +27718,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27749,7 +27749,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
@@ -27758,19 +27758,19 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>194.6244541931209</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,10 +27794,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>277.727050464421</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27840,25 +27840,25 @@
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>395.2029866510411</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>22.26478490148153</v>
+        <v>122.6068625706611</v>
       </c>
       <c r="K7" t="n">
-        <v>267.1509377355693</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L7" t="n">
-        <v>396.2015953708939</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1680042930194</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2386648669134</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U7" t="n">
+        <v>150.9482601269169</v>
+      </c>
+      <c r="V7" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W7" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X7" t="n">
+        <v>247.4436454301076</v>
+      </c>
+      <c r="Y7" t="n">
         <v>400</v>
-      </c>
-      <c r="V7" t="n">
-        <v>400</v>
-      </c>
-      <c r="W7" t="n">
-        <v>400</v>
-      </c>
-      <c r="X7" t="n">
-        <v>400</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27916,7 +27916,7 @@
         <v>400</v>
       </c>
       <c r="E8" t="n">
-        <v>400</v>
+        <v>398.0465935392086</v>
       </c>
       <c r="F8" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27992,7 +27992,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28001,13 +28001,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28034,19 +28034,19 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
+        <v>159.5184388018133</v>
+      </c>
+      <c r="S9" t="n">
+        <v>88.44885845517734</v>
+      </c>
+      <c r="T9" t="n">
+        <v>260.9224740732406</v>
+      </c>
+      <c r="U9" t="n">
         <v>400</v>
       </c>
-      <c r="S9" t="n">
-        <v>97.6862832515763</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>400</v>
-      </c>
-      <c r="U9" t="n">
-        <v>26.1959257979226</v>
-      </c>
-      <c r="V9" t="n">
-        <v>40.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28089,13 +28089,13 @@
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>99.98294672505649</v>
+        <v>122.6068625706611</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,13 +28116,13 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1680042930194</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2386648669134</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9483584875727</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
@@ -28134,7 +28134,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28165,7 +28165,7 @@
         <v>321</v>
       </c>
       <c r="I11" t="n">
-        <v>96.3057582470187</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28223,10 +28223,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D12" t="n">
         <v>321</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>321</v>
@@ -28283,16 +28283,16 @@
         <v>321</v>
       </c>
       <c r="V12" t="n">
-        <v>147.4081841180268</v>
+        <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -28460,19 +28460,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D15" t="n">
         <v>321</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>321</v>
@@ -28520,16 +28520,16 @@
         <v>321</v>
       </c>
       <c r="V15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
     </row>
     <row r="16">
@@ -28639,7 +28639,7 @@
         <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S17" t="n">
         <v>321</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C18" t="n">
         <v>321</v>
@@ -28706,7 +28706,7 @@
         <v>321</v>
       </c>
       <c r="E18" t="n">
-        <v>321</v>
+        <v>226.0367322273741</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -28742,16 +28742,16 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>321</v>
       </c>
       <c r="S18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="U18" t="n">
         <v>321</v>
@@ -28937,7 +28937,7 @@
         <v>321</v>
       </c>
       <c r="C21" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -28952,7 +28952,7 @@
         <v>321</v>
       </c>
       <c r="H21" t="n">
-        <v>226.0367322273743</v>
+        <v>321</v>
       </c>
       <c r="I21" t="n">
         <v>191.6509141932353</v>
@@ -29171,16 +29171,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>147.4081841180268</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F24" t="n">
         <v>321</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>321</v>
@@ -29231,16 +29231,16 @@
         <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25">
@@ -29408,13 +29408,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E27" t="n">
         <v>321</v>
@@ -29453,7 +29453,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>321</v>
@@ -29468,16 +29468,16 @@
         <v>321</v>
       </c>
       <c r="V27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>321</v>
       </c>
       <c r="X27" t="n">
-        <v>147.4081841180269</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -29614,10 +29614,10 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S29" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T29" t="n">
         <v>321</v>
@@ -29645,25 +29645,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D30" t="n">
         <v>321</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F30" t="n">
         <v>321</v>
       </c>
       <c r="G30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>191.6509141932353</v>
@@ -29690,13 +29690,13 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>321</v>
+        <v>226.036732227374</v>
       </c>
       <c r="T30" t="n">
         <v>321</v>
@@ -29714,7 +29714,7 @@
         <v>321</v>
       </c>
       <c r="Y30" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31">
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="C33" t="n">
         <v>321</v>
@@ -29897,7 +29897,7 @@
         <v>321</v>
       </c>
       <c r="G33" t="n">
-        <v>147.4081841180267</v>
+        <v>321</v>
       </c>
       <c r="H33" t="n">
         <v>321</v>
@@ -29927,16 +29927,16 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U33" t="n">
         <v>321</v>
@@ -29945,13 +29945,13 @@
         <v>321</v>
       </c>
       <c r="W33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -30061,7 +30061,7 @@
         <v>321</v>
       </c>
       <c r="I35" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S35" t="n">
         <v>321</v>
@@ -30134,13 +30134,13 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>18.05909831126212</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>321</v>
@@ -30182,13 +30182,13 @@
         <v>321</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y36" t="n">
-        <v>321</v>
+        <v>226.0367322273746</v>
       </c>
     </row>
     <row r="37">
@@ -30298,7 +30298,7 @@
         <v>321</v>
       </c>
       <c r="I38" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30328,7 +30328,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S38" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T38" t="n">
         <v>321</v>
@@ -30356,16 +30356,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>321</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -30377,7 +30377,7 @@
         <v>321</v>
       </c>
       <c r="I39" t="n">
-        <v>191.6509141932353</v>
+        <v>96.68764642060964</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>321</v>
@@ -30419,13 +30419,13 @@
         <v>321</v>
       </c>
       <c r="W39" t="n">
-        <v>147.4081841180267</v>
+        <v>321</v>
       </c>
       <c r="X39" t="n">
         <v>321</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40">
@@ -30532,10 +30532,10 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I41" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30596,16 +30596,16 @@
         <v>321</v>
       </c>
       <c r="C42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G42" t="n">
         <v>321</v>
@@ -30641,7 +30641,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>226.0367322273743</v>
+        <v>226.0367322273741</v>
       </c>
       <c r="S42" t="n">
         <v>321</v>
@@ -30653,13 +30653,13 @@
         <v>321</v>
       </c>
       <c r="V42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>321</v>
       </c>
       <c r="X42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>321</v>
@@ -30799,10 +30799,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S44" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T44" t="n">
         <v>321</v>
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="C45" t="n">
         <v>321</v>
@@ -30845,7 +30845,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="H45" t="n">
         <v>321</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>321</v>
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H8" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I8" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J8" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M8" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N8" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O8" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P8" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R8" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S8" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T8" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H9" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I9" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J9" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K9" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L9" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M9" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O9" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P9" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R9" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S9" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H10" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I10" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J10" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K10" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L10" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M10" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N10" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O10" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P10" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R10" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S10" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T10" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="K2" t="n">
-        <v>300.210210236103</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>374</v>
+        <v>65.34340703517586</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>180.6578102564064</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="P2" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M3" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>191.6878519954473</v>
+        <v>188.4896145353295</v>
       </c>
       <c r="O3" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,7 +34877,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>127.2747533519553</v>
@@ -34886,28 +34886,28 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,19 +34928,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698065</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>114.8369995486488</v>
+        <v>52.44465182451974</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
         <v>152.5563545698924</v>
@@ -34980,25 +34980,25 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>52.1599296482412</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512562</v>
+        <v>65.34340703517586</v>
       </c>
       <c r="M5" t="n">
-        <v>242.0199542155221</v>
+        <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>374</v>
+        <v>181.6174062160025</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>374</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q5" t="n">
         <v>374</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M6" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35126,19 +35126,19 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>120.8201306832991</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>100.4695694724582</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -35171,19 +35171,19 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35217,25 +35217,25 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>52.1599296482412</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>248.0502805878618</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>374</v>
+        <v>246.9608132511784</v>
       </c>
       <c r="N8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
         <v>374</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K9" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L9" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M9" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O9" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P9" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35366,22 +35366,22 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>155.1400615846995</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8642181606765</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I10" t="n">
-        <v>228.8979542159473</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J10" t="n">
-        <v>77.71816182357495</v>
+        <v>100.4695694724582</v>
       </c>
       <c r="K10" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35420,7 +35420,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,7 +35454,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>261.4423154327527</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K11" t="n">
         <v>649</v>
@@ -35466,7 +35466,7 @@
         <v>649</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
@@ -35606,7 +35606,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H13" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I13" t="n">
         <v>163.0214951995539</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K14" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L14" t="n">
-        <v>218.2342914572864</v>
+        <v>649.0000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>649</v>
+        <v>278.5269147425624</v>
       </c>
       <c r="N14" t="n">
-        <v>609.8778844919133</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>162.757678164601</v>
@@ -35712,7 +35712,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35931,19 +35931,19 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K17" t="n">
-        <v>648.9999999999999</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L17" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N17" t="n">
-        <v>236.2045428832663</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>162.757678164601</v>
+        <v>223.0503014498773</v>
       </c>
       <c r="P17" t="n">
         <v>198.5777841804241</v>
@@ -36165,7 +36165,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K20" t="n">
         <v>175.9119195979899</v>
@@ -36174,16 +36174,16 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M20" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.355038036034114</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>649</v>
       </c>
       <c r="P20" t="n">
-        <v>198.5777841804241</v>
+        <v>421.6280856303015</v>
       </c>
       <c r="Q20" t="n">
         <v>592.3686050224903</v>
@@ -36368,7 +36368,7 @@
         <v>73.55635456989245</v>
       </c>
       <c r="Y22" t="n">
-        <v>33.53464715053764</v>
+        <v>33.53464715053765</v>
       </c>
     </row>
     <row r="23">
@@ -36402,28 +36402,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K23" t="n">
-        <v>649</v>
+        <v>434.7823270636903</v>
       </c>
       <c r="L23" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M23" t="n">
-        <v>179.1121759491996</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P23" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36642,16 +36642,16 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K26" t="n">
-        <v>648.9999999999999</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L26" t="n">
-        <v>218.2342914572864</v>
+        <v>649.0000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>179.5731479057567</v>
+        <v>649</v>
       </c>
       <c r="N26" t="n">
-        <v>649</v>
+        <v>221.8955197650528</v>
       </c>
       <c r="O26" t="n">
         <v>162.757678164601</v>
@@ -36791,7 +36791,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H28" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I28" t="n">
         <v>163.0214951995539</v>
@@ -36879,7 +36879,7 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K29" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L29" t="n">
         <v>649</v>
@@ -36888,7 +36888,7 @@
         <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>649</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
@@ -36897,7 +36897,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.200256351209361</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K32" t="n">
-        <v>609.8778844919133</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L32" t="n">
-        <v>218.2342914572864</v>
+        <v>441.2845929071638</v>
       </c>
       <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
         <v>649</v>
-      </c>
-      <c r="N32" t="n">
-        <v>649</v>
-      </c>
-      <c r="O32" t="n">
-        <v>162.757678164601</v>
       </c>
       <c r="P32" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37265,7 +37265,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H34" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I34" t="n">
         <v>163.0214951995539</v>
@@ -37350,10 +37350,10 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>512.6348760697097</v>
+        <v>99.83941895297586</v>
       </c>
       <c r="K35" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L35" t="n">
         <v>218.2342914572864</v>
@@ -37362,7 +37362,7 @@
         <v>649</v>
       </c>
       <c r="N35" t="n">
-        <v>60.29262328527629</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>162.757678164601</v>
@@ -37593,22 +37593,22 @@
         <v>175.9119195979899</v>
       </c>
       <c r="L38" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M38" t="n">
-        <v>146.3014272389486</v>
+        <v>649</v>
       </c>
       <c r="N38" t="n">
         <v>649</v>
       </c>
       <c r="O38" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P38" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.200256351209361</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37739,7 +37739,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H40" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I40" t="n">
         <v>163.0214951995539</v>
@@ -37833,16 +37833,16 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>421.6280856303014</v>
+      </c>
+      <c r="P41" t="n">
         <v>649</v>
-      </c>
-      <c r="N41" t="n">
-        <v>60.29262328527629</v>
-      </c>
-      <c r="O41" t="n">
-        <v>162.757678164601</v>
-      </c>
-      <c r="P41" t="n">
-        <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
         <v>592.3686050224903</v>
@@ -37976,7 +37976,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H43" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I43" t="n">
         <v>163.0214951995539</v>
@@ -38067,10 +38067,10 @@
         <v>175.9119195979899</v>
       </c>
       <c r="L44" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M44" t="n">
-        <v>59.83165132871935</v>
+        <v>490.597359871433</v>
       </c>
       <c r="N44" t="n">
         <v>649</v>
@@ -38213,7 +38213,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
